--- a/data/SkillPermission.xlsx
+++ b/data/SkillPermission.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,31 +427,6 @@
           <t>skilltype</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>skilltype</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>skilltype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>skilltype</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>skilltype</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>skilltype</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -461,124 +436,65 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>uint32</t>
+          <t>repeated uint32</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
     </row>
+    <row r="4"/>
     <row r="5"/>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -586,10 +502,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -604,29 +520,6 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/SkillPermission.xlsx
+++ b/data/SkillPermission.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>skilltype</t>
+          <t>skill_type</t>
         </is>
       </c>
     </row>
@@ -452,8 +452,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
         <v>1</v>
